--- a/linkedin-follow-client/follow-list.xlsx
+++ b/linkedin-follow-client/follow-list.xlsx
@@ -399,13 +399,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:F259"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="70.83203125" customWidth="1"/>
     <col min="3" max="3" width="25.83203125" customWidth="1"/>
     <col min="4" max="4" width="25.83203125" customWidth="1"/>
     <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -424,6 +425,9 @@
       <c r="E1" s="1" t="str">
         <v>abhi_00</v>
       </c>
+      <c r="F1" s="1" t="str">
+        <v>mohit_00</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
@@ -441,6 +445,9 @@
       <c r="E2" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
@@ -458,6 +465,9 @@
       <c r="E3" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F3" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
@@ -475,6 +485,9 @@
       <c r="E4" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F4" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
@@ -492,6 +505,9 @@
       <c r="E5" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F5" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
@@ -509,6 +525,9 @@
       <c r="E6" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F6" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
@@ -526,6 +545,9 @@
       <c r="E7" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F7" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
@@ -543,6 +565,9 @@
       <c r="E8" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F8" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
@@ -560,6 +585,9 @@
       <c r="E9" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F9" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
@@ -577,6 +605,9 @@
       <c r="E10" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F10" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
@@ -594,6 +625,9 @@
       <c r="E11" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F11" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
@@ -611,6 +645,9 @@
       <c r="E12" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F12" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="str">
@@ -628,6 +665,9 @@
       <c r="E13" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F13" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
@@ -645,6 +685,9 @@
       <c r="E14" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F14" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="str">
@@ -662,6 +705,9 @@
       <c r="E15" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F15" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="str">
@@ -679,6 +725,9 @@
       <c r="E16" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F16" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="str">
@@ -696,6 +745,9 @@
       <c r="E17" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F17" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="str">
@@ -713,6 +765,9 @@
       <c r="E18" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F18" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="str">
@@ -730,6 +785,9 @@
       <c r="E19" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F19" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="str">
@@ -747,6 +805,9 @@
       <c r="E20" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F20" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="str">
@@ -764,6 +825,9 @@
       <c r="E21" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F21" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="str">
@@ -781,6 +845,9 @@
       <c r="E22" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F22" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="str">
@@ -798,6 +865,9 @@
       <c r="E23" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F23" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="str">
@@ -815,6 +885,9 @@
       <c r="E24" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F24" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="str">
@@ -832,6 +905,9 @@
       <c r="E25" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F25" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="str">
@@ -849,6 +925,9 @@
       <c r="E26" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F26" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="str">
@@ -866,6 +945,9 @@
       <c r="E27" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F27" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="str">
@@ -883,6 +965,9 @@
       <c r="E28" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F28" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="str">
@@ -900,6 +985,9 @@
       <c r="E29" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F29" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="str">
@@ -917,6 +1005,9 @@
       <c r="E30" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F30" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="str">
@@ -934,6 +1025,9 @@
       <c r="E31" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F31" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="str">
@@ -951,6 +1045,9 @@
       <c r="E32" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F32" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="str">
@@ -968,6 +1065,9 @@
       <c r="E33" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F33" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="str">
@@ -985,6 +1085,9 @@
       <c r="E34" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F34" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="str">
@@ -1002,6 +1105,9 @@
       <c r="E35" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F35" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="str">
@@ -1019,6 +1125,9 @@
       <c r="E36" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F36" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="str">
@@ -1036,6 +1145,9 @@
       <c r="E37" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F37" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="str">
@@ -1053,6 +1165,9 @@
       <c r="E38" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F38" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="str">
@@ -1070,6 +1185,9 @@
       <c r="E39" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F39" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="str">
@@ -1087,6 +1205,9 @@
       <c r="E40" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F40" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="str">
@@ -1104,6 +1225,9 @@
       <c r="E41" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F41" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="str">
@@ -1121,6 +1245,9 @@
       <c r="E42" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F42" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="str">
@@ -1138,6 +1265,9 @@
       <c r="E43" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F43" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="str">
@@ -1155,6 +1285,9 @@
       <c r="E44" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F44" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="str">
@@ -1172,6 +1305,9 @@
       <c r="E45" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F45" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="str">
@@ -1189,6 +1325,9 @@
       <c r="E46" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F46" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="str">
@@ -1206,6 +1345,9 @@
       <c r="E47" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F47" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="str">
@@ -1223,6 +1365,9 @@
       <c r="E48" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F48" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="str">
@@ -1240,6 +1385,9 @@
       <c r="E49" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F49" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="str">
@@ -1257,6 +1405,9 @@
       <c r="E50" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F50" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="str">
@@ -1274,6 +1425,9 @@
       <c r="E51" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F51" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="str">
@@ -1291,6 +1445,9 @@
       <c r="E52" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F52" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="str">
@@ -1308,6 +1465,9 @@
       <c r="E53" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F53" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="str">
@@ -1325,6 +1485,9 @@
       <c r="E54" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F54" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="str">
@@ -1342,6 +1505,9 @@
       <c r="E55" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F55" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="str">
@@ -1359,6 +1525,9 @@
       <c r="E56" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F56" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="str">
@@ -1376,6 +1545,9 @@
       <c r="E57" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F57" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="str">
@@ -1393,6 +1565,9 @@
       <c r="E58" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F58" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="str">
@@ -1410,6 +1585,9 @@
       <c r="E59" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F59" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="str">
@@ -1427,6 +1605,9 @@
       <c r="E60" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F60" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="str">
@@ -1444,6 +1625,9 @@
       <c r="E61" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F61" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="str">
@@ -1461,6 +1645,9 @@
       <c r="E62" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F62" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="str">
@@ -1478,6 +1665,9 @@
       <c r="E63" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F63" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="str">
@@ -1495,6 +1685,9 @@
       <c r="E64" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F64" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="str">
@@ -1512,6 +1705,9 @@
       <c r="E65" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F65" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="str">
@@ -1529,6 +1725,9 @@
       <c r="E66" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F66" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="str">
@@ -1546,6 +1745,9 @@
       <c r="E67" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F67" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="str">
@@ -1563,6 +1765,9 @@
       <c r="E68" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F68" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="str">
@@ -1580,6 +1785,9 @@
       <c r="E69" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F69" s="1" t="str">
+        <v>Followed</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="str">
@@ -1597,6 +1805,9 @@
       <c r="E70" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F70" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="str">
@@ -1614,6 +1825,9 @@
       <c r="E71" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F71" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="str">
@@ -1631,6 +1845,9 @@
       <c r="E72" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F72" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="str">
@@ -1648,6 +1865,9 @@
       <c r="E73" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F73" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="str">
@@ -1665,6 +1885,9 @@
       <c r="E74" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F74" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="str">
@@ -1682,6 +1905,9 @@
       <c r="E75" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F75" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="str">
@@ -1699,6 +1925,9 @@
       <c r="E76" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F76" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="str">
@@ -1716,6 +1945,9 @@
       <c r="E77" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F77" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="str">
@@ -1733,6 +1965,9 @@
       <c r="E78" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F78" s="1" t="str">
+        <v>Followed</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="str">
@@ -1750,6 +1985,9 @@
       <c r="E79" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F79" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="str">
@@ -1767,6 +2005,9 @@
       <c r="E80" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F80" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="str">
@@ -1784,6 +2025,9 @@
       <c r="E81" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F81" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="str">
@@ -1801,6 +2045,9 @@
       <c r="E82" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F82" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="str">
@@ -1818,6 +2065,9 @@
       <c r="E83" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F83" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="str">
@@ -1835,6 +2085,9 @@
       <c r="E84" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F84" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="str">
@@ -1852,6 +2105,9 @@
       <c r="E85" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F85" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="str">
@@ -1869,6 +2125,9 @@
       <c r="E86" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F86" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="str">
@@ -1886,6 +2145,9 @@
       <c r="E87" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F87" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="str">
@@ -1903,6 +2165,9 @@
       <c r="E88" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F88" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="str">
@@ -1920,6 +2185,9 @@
       <c r="E89" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F89" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="str">
@@ -1937,6 +2205,9 @@
       <c r="E90" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F90" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="str">
@@ -1954,6 +2225,9 @@
       <c r="E91" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F91" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="str">
@@ -1971,6 +2245,9 @@
       <c r="E92" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F92" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="str">
@@ -1988,6 +2265,9 @@
       <c r="E93" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F93" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="str">
@@ -2005,6 +2285,9 @@
       <c r="E94" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F94" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="str">
@@ -2022,6 +2305,9 @@
       <c r="E95" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F95" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="str">
@@ -2039,6 +2325,9 @@
       <c r="E96" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F96" s="1" t="str">
+        <v>Followed</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="str">
@@ -2056,6 +2345,9 @@
       <c r="E97" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F97" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="str">
@@ -2073,6 +2365,9 @@
       <c r="E98" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F98" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="str">
@@ -2090,6 +2385,9 @@
       <c r="E99" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F99" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="str">
@@ -2107,6 +2405,9 @@
       <c r="E100" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F100" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="str">
@@ -2124,6 +2425,9 @@
       <c r="E101" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F101" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="str">
@@ -2141,6 +2445,9 @@
       <c r="E102" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F102" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="str">
@@ -2158,6 +2465,9 @@
       <c r="E103" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F103" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="str">
@@ -2175,6 +2485,9 @@
       <c r="E104" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F104" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="str">
@@ -2192,6 +2505,9 @@
       <c r="E105" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F105" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="str">
@@ -2209,6 +2525,9 @@
       <c r="E106" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F106" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="str">
@@ -2226,6 +2545,9 @@
       <c r="E107" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F107" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="str">
@@ -2243,6 +2565,9 @@
       <c r="E108" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F108" s="1" t="str">
+        <v>Followed</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="str">
@@ -2260,6 +2585,9 @@
       <c r="E109" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F109" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="str">
@@ -2277,6 +2605,9 @@
       <c r="E110" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F110" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="str">
@@ -2294,6 +2625,9 @@
       <c r="E111" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F111" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="str">
@@ -2311,6 +2645,9 @@
       <c r="E112" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F112" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="str">
@@ -2328,6 +2665,9 @@
       <c r="E113" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F113" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="str">
@@ -2345,6 +2685,9 @@
       <c r="E114" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F114" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="str">
@@ -2362,6 +2705,9 @@
       <c r="E115" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F115" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="str">
@@ -2379,6 +2725,9 @@
       <c r="E116" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F116" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="str">
@@ -2396,6 +2745,9 @@
       <c r="E117" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F117" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="str">
@@ -2413,6 +2765,9 @@
       <c r="E118" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F118" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="str">
@@ -2430,6 +2785,9 @@
       <c r="E119" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F119" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="str">
@@ -2447,6 +2805,9 @@
       <c r="E120" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F120" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="str">
@@ -2464,6 +2825,9 @@
       <c r="E121" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F121" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="str">
@@ -2481,6 +2845,9 @@
       <c r="E122" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F122" s="1" t="str">
+        <v>Followed</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="str">
@@ -2498,6 +2865,9 @@
       <c r="E123" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F123" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="str">
@@ -2515,6 +2885,9 @@
       <c r="E124" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F124" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="str">
@@ -2532,6 +2905,9 @@
       <c r="E125" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F125" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="str">
@@ -2549,6 +2925,9 @@
       <c r="E126" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F126" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="str">
@@ -2566,6 +2945,9 @@
       <c r="E127" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F127" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="str">
@@ -2583,6 +2965,9 @@
       <c r="E128" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F128" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="str">
@@ -2600,6 +2985,9 @@
       <c r="E129" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F129" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="str">
@@ -2617,6 +3005,9 @@
       <c r="E130" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F130" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="str">
@@ -2634,6 +3025,9 @@
       <c r="E131" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F131" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="str">
@@ -2651,6 +3045,9 @@
       <c r="E132" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F132" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="str">
@@ -2668,6 +3065,9 @@
       <c r="E133" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F133" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="str">
@@ -2685,6 +3085,9 @@
       <c r="E134" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F134" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="str">
@@ -2702,6 +3105,9 @@
       <c r="E135" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F135" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="str">
@@ -2719,6 +3125,9 @@
       <c r="E136" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F136" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="str">
@@ -2736,6 +3145,9 @@
       <c r="E137" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F137" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="str">
@@ -2753,6 +3165,9 @@
       <c r="E138" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F138" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="str">
@@ -2770,6 +3185,9 @@
       <c r="E139" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F139" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="str">
@@ -2787,6 +3205,9 @@
       <c r="E140" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F140" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="str">
@@ -2804,6 +3225,9 @@
       <c r="E141" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F141" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="str">
@@ -2821,6 +3245,9 @@
       <c r="E142" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F142" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="str">
@@ -2838,6 +3265,9 @@
       <c r="E143" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F143" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="str">
@@ -2855,6 +3285,9 @@
       <c r="E144" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F144" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="str">
@@ -2872,6 +3305,9 @@
       <c r="E145" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F145" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="str">
@@ -2889,6 +3325,9 @@
       <c r="E146" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F146" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="str">
@@ -2906,6 +3345,9 @@
       <c r="E147" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F147" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="str">
@@ -2923,6 +3365,9 @@
       <c r="E148" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F148" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="str">
@@ -2940,6 +3385,9 @@
       <c r="E149" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F149" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="str">
@@ -2957,6 +3405,9 @@
       <c r="E150" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F150" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="str">
@@ -2974,6 +3425,9 @@
       <c r="E151" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F151" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="str">
@@ -2991,6 +3445,9 @@
       <c r="E152" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F152" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="str">
@@ -3008,6 +3465,9 @@
       <c r="E153" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F153" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="str">
@@ -3025,6 +3485,9 @@
       <c r="E154" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F154" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="str">
@@ -3042,6 +3505,9 @@
       <c r="E155" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F155" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="str">
@@ -3059,6 +3525,9 @@
       <c r="E156" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F156" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="str">
@@ -3076,6 +3545,9 @@
       <c r="E157" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F157" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="str">
@@ -3093,6 +3565,9 @@
       <c r="E158" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F158" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="str">
@@ -3110,6 +3585,9 @@
       <c r="E159" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F159" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="str">
@@ -3127,6 +3605,9 @@
       <c r="E160" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F160" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="str">
@@ -3144,6 +3625,9 @@
       <c r="E161" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F161" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="str">
@@ -3161,6 +3645,9 @@
       <c r="E162" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F162" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="str">
@@ -3178,6 +3665,9 @@
       <c r="E163" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F163" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="str">
@@ -3195,6 +3685,9 @@
       <c r="E164" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F164" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="str">
@@ -3212,6 +3705,9 @@
       <c r="E165" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F165" s="1" t="str">
+        <v>Followed</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="str">
@@ -3229,6 +3725,9 @@
       <c r="E166" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F166" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="str">
@@ -3246,6 +3745,9 @@
       <c r="E167" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F167" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="str">
@@ -3263,6 +3765,9 @@
       <c r="E168" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F168" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="str">
@@ -3280,6 +3785,9 @@
       <c r="E169" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F169" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="str">
@@ -3297,6 +3805,9 @@
       <c r="E170" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F170" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="str">
@@ -3314,6 +3825,9 @@
       <c r="E171" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F171" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="str">
@@ -3331,6 +3845,9 @@
       <c r="E172" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F172" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="str">
@@ -3348,6 +3865,9 @@
       <c r="E173" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F173" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="str">
@@ -3365,6 +3885,9 @@
       <c r="E174" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F174" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="str">
@@ -3382,6 +3905,9 @@
       <c r="E175" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F175" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="str">
@@ -3399,6 +3925,9 @@
       <c r="E176" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F176" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="str">
@@ -3416,6 +3945,9 @@
       <c r="E177" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F177" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="str">
@@ -3433,6 +3965,9 @@
       <c r="E178" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F178" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="str">
@@ -3450,6 +3985,9 @@
       <c r="E179" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F179" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="str">
@@ -3467,6 +4005,9 @@
       <c r="E180" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F180" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="str">
@@ -3484,6 +4025,9 @@
       <c r="E181" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F181" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="str">
@@ -3501,6 +4045,9 @@
       <c r="E182" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F182" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="str">
@@ -3518,6 +4065,9 @@
       <c r="E183" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F183" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="str">
@@ -3535,6 +4085,9 @@
       <c r="E184" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F184" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="str">
@@ -3552,6 +4105,9 @@
       <c r="E185" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F185" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="str">
@@ -3569,6 +4125,9 @@
       <c r="E186" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F186" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="str">
@@ -3586,6 +4145,9 @@
       <c r="E187" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F187" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="str">
@@ -3603,6 +4165,9 @@
       <c r="E188" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F188" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="str">
@@ -3620,6 +4185,9 @@
       <c r="E189" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F189" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="str">
@@ -3637,6 +4205,9 @@
       <c r="E190" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F190" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="str">
@@ -3654,6 +4225,9 @@
       <c r="E191" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F191" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="str">
@@ -3671,6 +4245,9 @@
       <c r="E192" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F192" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="str">
@@ -3688,6 +4265,9 @@
       <c r="E193" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F193" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="str">
@@ -3705,6 +4285,9 @@
       <c r="E194" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F194" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="str">
@@ -3722,6 +4305,9 @@
       <c r="E195" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F195" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="str">
@@ -3739,6 +4325,9 @@
       <c r="E196" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F196" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="str">
@@ -3756,6 +4345,9 @@
       <c r="E197" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F197" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="str">
@@ -3773,6 +4365,9 @@
       <c r="E198" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F198" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="str">
@@ -3790,6 +4385,9 @@
       <c r="E199" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F199" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="str">
@@ -3807,6 +4405,9 @@
       <c r="E200" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F200" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="str">
@@ -3824,6 +4425,9 @@
       <c r="E201" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F201" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="str">
@@ -3841,6 +4445,9 @@
       <c r="E202" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F202" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="str">
@@ -3858,6 +4465,9 @@
       <c r="E203" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F203" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="str">
@@ -3875,6 +4485,9 @@
       <c r="E204" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F204" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="str">
@@ -3892,6 +4505,9 @@
       <c r="E205" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F205" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="str">
@@ -3909,6 +4525,9 @@
       <c r="E206" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F206" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="str">
@@ -3926,6 +4545,9 @@
       <c r="E207" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F207" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="str">
@@ -3943,6 +4565,9 @@
       <c r="E208" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F208" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="str">
@@ -3960,6 +4585,9 @@
       <c r="E209" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F209" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="str">
@@ -3977,6 +4605,9 @@
       <c r="E210" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F210" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="str">
@@ -3994,6 +4625,9 @@
       <c r="E211" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F211" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="str">
@@ -4011,6 +4645,9 @@
       <c r="E212" s="1" t="str">
         <v>Failed (Page not found)</v>
       </c>
+      <c r="F212" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="str">
@@ -4028,6 +4665,9 @@
       <c r="E213" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F213" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="str">
@@ -4045,6 +4685,9 @@
       <c r="E214" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F214" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="str">
@@ -4062,6 +4705,9 @@
       <c r="E215" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F215" s="1" t="str">
+        <v>Already following</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="str">
@@ -4079,6 +4725,9 @@
       <c r="E216" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F216" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="str">
@@ -4096,6 +4745,9 @@
       <c r="E217" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F217" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="str">
@@ -4113,6 +4765,9 @@
       <c r="E218" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F218" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="str">
@@ -4130,6 +4785,9 @@
       <c r="E219" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F219" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="str">
@@ -4147,6 +4805,9 @@
       <c r="E220" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F220" s="1" t="str">
+        <v>Already following</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="str">
@@ -4164,6 +4825,9 @@
       <c r="E221" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F221" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="str">
@@ -4181,6 +4845,9 @@
       <c r="E222" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F222" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="str">
@@ -4198,6 +4865,9 @@
       <c r="E223" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F223" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="str">
@@ -4215,6 +4885,9 @@
       <c r="E224" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F224" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="str">
@@ -4232,6 +4905,9 @@
       <c r="E225" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F225" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="str">
@@ -4249,6 +4925,9 @@
       <c r="E226" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F226" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="str">
@@ -4266,6 +4945,9 @@
       <c r="E227" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F227" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="str">
@@ -4283,6 +4965,9 @@
       <c r="E228" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F228" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="str">
@@ -4300,6 +4985,9 @@
       <c r="E229" s="1" t="str">
         <v>Failed (Page not found)</v>
       </c>
+      <c r="F229" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="str">
@@ -4317,6 +5005,9 @@
       <c r="E230" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F230" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="str">
@@ -4334,6 +5025,9 @@
       <c r="E231" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F231" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="str">
@@ -4351,6 +5045,9 @@
       <c r="E232" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F232" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="str">
@@ -4368,6 +5065,9 @@
       <c r="E233" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F233" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="str">
@@ -4385,6 +5085,9 @@
       <c r="E234" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F234" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="str">
@@ -4402,6 +5105,9 @@
       <c r="E235" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F235" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="str">
@@ -4419,6 +5125,9 @@
       <c r="E236" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F236" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="str">
@@ -4436,6 +5145,9 @@
       <c r="E237" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F237" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="str">
@@ -4453,6 +5165,9 @@
       <c r="E238" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F238" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="str">
@@ -4470,6 +5185,9 @@
       <c r="E239" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F239" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="str">
@@ -4487,6 +5205,9 @@
       <c r="E240" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F240" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="str">
@@ -4504,6 +5225,9 @@
       <c r="E241" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F241" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="str">
@@ -4521,6 +5245,9 @@
       <c r="E242" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F242" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="str">
@@ -4538,6 +5265,9 @@
       <c r="E243" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F243" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="str">
@@ -4555,6 +5285,9 @@
       <c r="E244" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F244" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="str">
@@ -4572,6 +5305,9 @@
       <c r="E245" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F245" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="str">
@@ -4589,6 +5325,9 @@
       <c r="E246" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F246" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="str">
@@ -4606,6 +5345,9 @@
       <c r="E247" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F247" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="str">
@@ -4623,6 +5365,9 @@
       <c r="E248" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F248" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="str">
@@ -4640,6 +5385,9 @@
       <c r="E249" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F249" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="str">
@@ -4657,6 +5405,9 @@
       <c r="E250" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F250" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="str">
@@ -4674,6 +5425,9 @@
       <c r="E251" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F251" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="str">
@@ -4691,6 +5445,9 @@
       <c r="E252" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F252" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="str">
@@ -4708,6 +5465,9 @@
       <c r="E253" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F253" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="str">
@@ -4725,6 +5485,9 @@
       <c r="E254" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F254" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="str">
@@ -4742,6 +5505,9 @@
       <c r="E255" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F255" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="str">
@@ -4759,6 +5525,9 @@
       <c r="E256" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F256" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="str">
@@ -4776,6 +5545,9 @@
       <c r="E257" s="1" t="str">
         <v>Already following</v>
       </c>
+      <c r="F257" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="str">
@@ -4793,6 +5565,9 @@
       <c r="E258" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F258" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="str">
@@ -4810,10 +5585,13 @@
       <c r="E259" s="1" t="str">
         <v>Followed</v>
       </c>
+      <c r="F259" s="1" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E259"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F259"/>
   </ignoredErrors>
 </worksheet>
 </file>